--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.4173078459709</v>
+        <v>13.23031252497027</v>
       </c>
       <c r="D2" t="n">
-        <v>76.11642367496</v>
+        <v>12.368918847181</v>
       </c>
       <c r="E2" t="n">
-        <v>38.24863716696286</v>
+        <v>6.215403539631464</v>
       </c>
       <c r="F2" t="n">
-        <v>35.65909838332384</v>
+        <v>5.794603487290125</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.920033512045189</v>
+        <v>0.7995054457073433</v>
       </c>
       <c r="D3" t="n">
-        <v>4.798226908312316</v>
+        <v>0.7797118726007514</v>
       </c>
       <c r="E3" t="n">
-        <v>38.24863716696286</v>
+        <v>6.215403539631464</v>
       </c>
       <c r="F3" t="n">
-        <v>35.65909838332384</v>
+        <v>5.794603487290125</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
